--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/143.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/143.xlsx
@@ -426,13 +426,13 @@
         <v>-11.65704210332794</v>
       </c>
       <c r="E2">
-        <v>-11.9359591417428</v>
+        <v>-9.483256106656397</v>
       </c>
       <c r="F2">
-        <v>-5.904829138703348</v>
+        <v>-6.516162625234577</v>
       </c>
       <c r="G2">
-        <v>-13.46394687981944</v>
+        <v>-12.9165308433926</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-11.68593554710703</v>
       </c>
       <c r="E3">
-        <v>-12.12485084955075</v>
+        <v>-10.18779156429574</v>
       </c>
       <c r="F3">
-        <v>-5.967281413935209</v>
+        <v>-6.30603439381974</v>
       </c>
       <c r="G3">
-        <v>-14.06037616329048</v>
+        <v>-12.79096505675577</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-11.72955095253768</v>
       </c>
       <c r="E4">
-        <v>-12.22166962383474</v>
+        <v>-10.73095032219775</v>
       </c>
       <c r="F4">
-        <v>-6.113889190352276</v>
+        <v>-6.255945087890961</v>
       </c>
       <c r="G4">
-        <v>-13.57466513889978</v>
+        <v>-13.07081388111769</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-11.75946201452802</v>
       </c>
       <c r="E5">
-        <v>-13.80207082471963</v>
+        <v>-10.99001526322856</v>
       </c>
       <c r="F5">
-        <v>-5.884777677351183</v>
+        <v>-6.085081885552521</v>
       </c>
       <c r="G5">
-        <v>-13.7851358146088</v>
+        <v>-13.03749635740309</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-11.74519172020291</v>
       </c>
       <c r="E6">
-        <v>-13.67062280969899</v>
+        <v>-11.23498306467348</v>
       </c>
       <c r="F6">
-        <v>-5.944169963397102</v>
+        <v>-5.874579646255318</v>
       </c>
       <c r="G6">
-        <v>-13.80229332214314</v>
+        <v>-13.13365255520262</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-11.66544350600793</v>
       </c>
       <c r="E7">
-        <v>-15.20497395839988</v>
+        <v>-13.04215212996648</v>
       </c>
       <c r="F7">
-        <v>-5.33785141312242</v>
+        <v>-5.745320368355081</v>
       </c>
       <c r="G7">
-        <v>-14.5803743123666</v>
+        <v>-12.51158544707685</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-11.50180001099981</v>
       </c>
       <c r="E8">
-        <v>-15.46752129594258</v>
+        <v>-14.03045082587446</v>
       </c>
       <c r="F8">
-        <v>-5.450342049687788</v>
+        <v>-5.795156608042305</v>
       </c>
       <c r="G8">
-        <v>-14.07944990421554</v>
+        <v>-12.71969692448463</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-11.24733028646339</v>
       </c>
       <c r="E9">
-        <v>-15.95876562782066</v>
+        <v>-13.73830991069163</v>
       </c>
       <c r="F9">
-        <v>-5.235135511910087</v>
+        <v>-5.488036079984777</v>
       </c>
       <c r="G9">
-        <v>-13.96771774767333</v>
+        <v>-12.67586964811513</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-10.90441152851153</v>
       </c>
       <c r="E10">
-        <v>-16.69520871331805</v>
+        <v>-15.49791641348207</v>
       </c>
       <c r="F10">
-        <v>-5.328055140216914</v>
+        <v>-5.217114379062185</v>
       </c>
       <c r="G10">
-        <v>-14.00220010504153</v>
+        <v>-11.31667939788166</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-10.48600377795799</v>
       </c>
       <c r="E11">
-        <v>-17.03435066022649</v>
+        <v>-16.48631473581822</v>
       </c>
       <c r="F11">
-        <v>-5.18322089840924</v>
+        <v>-5.637167063510772</v>
       </c>
       <c r="G11">
-        <v>-13.60365473137748</v>
+        <v>-12.42972225039026</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-10.01699823685782</v>
       </c>
       <c r="E12">
-        <v>-17.24124758068893</v>
+        <v>-15.11135681523931</v>
       </c>
       <c r="F12">
-        <v>-5.122685465347458</v>
+        <v>-5.458337451859609</v>
       </c>
       <c r="G12">
-        <v>-13.57258812565265</v>
+        <v>-11.77894117239779</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-9.525147409743385</v>
       </c>
       <c r="E13">
-        <v>-18.2238087000292</v>
+        <v>-16.51173306042327</v>
       </c>
       <c r="F13">
-        <v>-5.038973140722748</v>
+        <v>-4.759207789407868</v>
       </c>
       <c r="G13">
-        <v>-13.05586791691442</v>
+        <v>-11.10839073450967</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-9.049521580195076</v>
       </c>
       <c r="E14">
-        <v>-19.60575405600195</v>
+        <v>-18.49502353682259</v>
       </c>
       <c r="F14">
-        <v>-4.600486796459664</v>
+        <v>-4.941942324995828</v>
       </c>
       <c r="G14">
-        <v>-12.71677991851828</v>
+        <v>-10.74713480325793</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-8.622314297214666</v>
       </c>
       <c r="E15">
-        <v>-19.95164795765582</v>
+        <v>-19.76988859640996</v>
       </c>
       <c r="F15">
-        <v>-4.11358320587035</v>
+        <v>-4.7379717626697</v>
       </c>
       <c r="G15">
-        <v>-11.76459239051834</v>
+        <v>-11.1131944428727</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-8.279456702488835</v>
       </c>
       <c r="E16">
-        <v>-20.36502970744601</v>
+        <v>-18.22753110566351</v>
       </c>
       <c r="F16">
-        <v>-4.189700229778791</v>
+        <v>-4.837959850024614</v>
       </c>
       <c r="G16">
-        <v>-12.14270395692095</v>
+        <v>-9.68059342268978</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-8.038412528813796</v>
       </c>
       <c r="E17">
-        <v>-21.4470225305727</v>
+        <v>-19.60416456162525</v>
       </c>
       <c r="F17">
-        <v>-3.834036543549809</v>
+        <v>-3.618446471664613</v>
       </c>
       <c r="G17">
-        <v>-11.57965946220648</v>
+        <v>-9.267536846679082</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-7.91242964064673</v>
       </c>
       <c r="E18">
-        <v>-21.644391541723</v>
+        <v>-20.58079338001547</v>
       </c>
       <c r="F18">
-        <v>-3.54549795307188</v>
+        <v>-3.485095887161949</v>
       </c>
       <c r="G18">
-        <v>-11.00028760901221</v>
+        <v>-9.52040090493613</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-7.889058489829865</v>
       </c>
       <c r="E19">
-        <v>-22.58038183436839</v>
+        <v>-22.13734310830197</v>
       </c>
       <c r="F19">
-        <v>-3.067197786328043</v>
+        <v>-3.711176403836198</v>
       </c>
       <c r="G19">
-        <v>-10.80998332100753</v>
+        <v>-8.606626637732608</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-7.952129903187112</v>
       </c>
       <c r="E20">
-        <v>-23.01705805445403</v>
+        <v>-21.65070423448969</v>
       </c>
       <c r="F20">
-        <v>-2.553286104937855</v>
+        <v>-2.98761238810408</v>
       </c>
       <c r="G20">
-        <v>-11.12633245399672</v>
+        <v>-8.300764288847409</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-8.065579649500632</v>
       </c>
       <c r="E21">
-        <v>-24.14944826481208</v>
+        <v>-22.23674764124434</v>
       </c>
       <c r="F21">
-        <v>-2.656873448657933</v>
+        <v>-2.9759895650754</v>
       </c>
       <c r="G21">
-        <v>-10.55540318387489</v>
+        <v>-8.766546814096825</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-8.198225470950145</v>
       </c>
       <c r="E22">
-        <v>-24.63423499275522</v>
+        <v>-22.36331848975873</v>
       </c>
       <c r="F22">
-        <v>-2.093909991510972</v>
+        <v>-2.618324543201255</v>
       </c>
       <c r="G22">
-        <v>-11.08739747897235</v>
+        <v>-9.047048601549076</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-8.310295608032106</v>
       </c>
       <c r="E23">
-        <v>-25.29005312702005</v>
+        <v>-23.95016370915653</v>
       </c>
       <c r="F23">
-        <v>-2.040567272607698</v>
+        <v>-1.936841591531352</v>
       </c>
       <c r="G23">
-        <v>-10.58575776452132</v>
+        <v>-8.080410573801339</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-8.373846743960177</v>
       </c>
       <c r="E24">
-        <v>-25.22342568894519</v>
+        <v>-23.88314682231702</v>
       </c>
       <c r="F24">
-        <v>-1.905676753103229</v>
+        <v>-1.322183038245285</v>
       </c>
       <c r="G24">
-        <v>-10.86252880306048</v>
+        <v>-10.31945054153523</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-8.361630225795247</v>
       </c>
       <c r="E25">
-        <v>-25.93373495094432</v>
+        <v>-23.35051223800884</v>
       </c>
       <c r="F25">
-        <v>-1.513091074996668</v>
+        <v>-1.67506009653125</v>
       </c>
       <c r="G25">
-        <v>-10.80230198133687</v>
+        <v>-9.793470725556237</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-8.261731180211326</v>
       </c>
       <c r="E26">
-        <v>-26.37193273829654</v>
+        <v>-24.68282099038352</v>
       </c>
       <c r="F26">
-        <v>-1.505476721830135</v>
+        <v>-1.633998752741881</v>
       </c>
       <c r="G26">
-        <v>-10.44267025475705</v>
+        <v>-10.02632917596535</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-8.069443803626649</v>
       </c>
       <c r="E27">
-        <v>-25.73488965726752</v>
+        <v>-25.19783528232785</v>
       </c>
       <c r="F27">
-        <v>-1.272765952463878</v>
+        <v>-2.404022582627412</v>
       </c>
       <c r="G27">
-        <v>-10.9245504529771</v>
+        <v>-10.39171944638199</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-7.79327375169842</v>
       </c>
       <c r="E28">
-        <v>-26.11337045788059</v>
+        <v>-25.88367719926353</v>
       </c>
       <c r="F28">
-        <v>-1.465450837294266</v>
+        <v>-1.806136812513229</v>
       </c>
       <c r="G28">
-        <v>-11.3827861686398</v>
+        <v>-9.676324553440942</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-7.447807292619134</v>
       </c>
       <c r="E29">
-        <v>-26.26568115265457</v>
+        <v>-25.26297738092819</v>
       </c>
       <c r="F29">
-        <v>-1.530663232712254</v>
+        <v>-1.681136171430784</v>
       </c>
       <c r="G29">
-        <v>-11.09575146906269</v>
+        <v>-10.02630948863599</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-7.053548691091196</v>
       </c>
       <c r="E30">
-        <v>-25.85022083329486</v>
+        <v>-25.15513177243552</v>
       </c>
       <c r="F30">
-        <v>-1.275342175086585</v>
+        <v>-1.237801392759114</v>
       </c>
       <c r="G30">
-        <v>-10.66714518408178</v>
+        <v>-10.12799126354163</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-6.636116275084925</v>
       </c>
       <c r="E31">
-        <v>-26.35281804951017</v>
+        <v>-23.58610156978389</v>
       </c>
       <c r="F31">
-        <v>-1.50725356990914</v>
+        <v>-2.09654585658668</v>
       </c>
       <c r="G31">
-        <v>-11.36331539990605</v>
+        <v>-9.597171645762458</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-6.218989994559803</v>
       </c>
       <c r="E32">
-        <v>-26.02835741533459</v>
+        <v>-24.30452585720476</v>
       </c>
       <c r="F32">
-        <v>-1.512675234560463</v>
+        <v>-1.47681769479548</v>
       </c>
       <c r="G32">
-        <v>-11.24507986223302</v>
+        <v>-9.386113631394295</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-5.826916642280692</v>
       </c>
       <c r="E33">
-        <v>-25.54394202226009</v>
+        <v>-24.41404247260625</v>
       </c>
       <c r="F33">
-        <v>-1.633535695363716</v>
+        <v>-1.508686645515983</v>
       </c>
       <c r="G33">
-        <v>-10.85644869951083</v>
+        <v>-10.05096786865522</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-5.474423111540131</v>
       </c>
       <c r="E34">
-        <v>-26.67047691572622</v>
+        <v>-24.41337225845312</v>
       </c>
       <c r="F34">
-        <v>-1.837515369731275</v>
+        <v>-1.904473135266961</v>
       </c>
       <c r="G34">
-        <v>-10.75036352527242</v>
+        <v>-8.856117600226547</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-5.176814716359332</v>
       </c>
       <c r="E35">
-        <v>-24.92612231339362</v>
+        <v>-24.3542032170689</v>
       </c>
       <c r="F35">
-        <v>-2.257793370113423</v>
+        <v>-1.729806069814866</v>
       </c>
       <c r="G35">
-        <v>-11.21099453267351</v>
+        <v>-9.516282971879026</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-4.935432612051394</v>
       </c>
       <c r="E36">
-        <v>-25.19347889033247</v>
+        <v>-22.54237888049602</v>
       </c>
       <c r="F36">
-        <v>-1.900499456835732</v>
+        <v>-1.557833683524078</v>
       </c>
       <c r="G36">
-        <v>-10.36872136447185</v>
+        <v>-9.24166769590442</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-4.753973590923818</v>
       </c>
       <c r="E37">
-        <v>-24.03969164028818</v>
+        <v>-23.79274036722789</v>
       </c>
       <c r="F37">
-        <v>-1.710772672000742</v>
+        <v>-2.174890360441249</v>
       </c>
       <c r="G37">
-        <v>-10.64225055611028</v>
+        <v>-8.552201015726098</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-4.62642543995372</v>
       </c>
       <c r="E38">
-        <v>-24.26823466650729</v>
+        <v>-23.08212316899624</v>
       </c>
       <c r="F38">
-        <v>-2.123669918823947</v>
+        <v>-1.977152434453785</v>
       </c>
       <c r="G38">
-        <v>-10.27155126921045</v>
+        <v>-7.895546551142225</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-4.552053536757683</v>
       </c>
       <c r="E39">
-        <v>-24.13837161738932</v>
+        <v>-22.67832367020629</v>
       </c>
       <c r="F39">
-        <v>-1.885655112977565</v>
+        <v>-1.638025446686889</v>
       </c>
       <c r="G39">
-        <v>-10.37071306595843</v>
+        <v>-7.509881612709771</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.519815021936699</v>
       </c>
       <c r="E40">
-        <v>-24.46732902625451</v>
+        <v>-22.16470414825631</v>
       </c>
       <c r="F40">
-        <v>-1.957056241261869</v>
+        <v>-2.144680629628554</v>
       </c>
       <c r="G40">
-        <v>-10.07009410912522</v>
+        <v>-8.961290594871429</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.522996668626724</v>
       </c>
       <c r="E41">
-        <v>-22.31664350816167</v>
+        <v>-22.3239841645281</v>
       </c>
       <c r="F41">
-        <v>-1.799180183064519</v>
+        <v>-2.316331609367056</v>
       </c>
       <c r="G41">
-        <v>-9.838587521998603</v>
+        <v>-7.517208580452011</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.547946497671622</v>
       </c>
       <c r="E42">
-        <v>-23.01136576262639</v>
+        <v>-19.96867049145066</v>
       </c>
       <c r="F42">
-        <v>-1.802894582498672</v>
+        <v>-2.113654128556698</v>
       </c>
       <c r="G42">
-        <v>-9.746463945495632</v>
+        <v>-7.487999146129835</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-4.58721521191117</v>
       </c>
       <c r="E43">
-        <v>-21.94594715436778</v>
+        <v>-21.51809693012309</v>
       </c>
       <c r="F43">
-        <v>-2.19065005027951</v>
+        <v>-2.028234538714819</v>
       </c>
       <c r="G43">
-        <v>-9.986216242401138</v>
+        <v>-7.899021364773676</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.629670878408532</v>
       </c>
       <c r="E44">
-        <v>-21.49966151243786</v>
+        <v>-20.31895701289197</v>
       </c>
       <c r="F44">
-        <v>-2.263924117261543</v>
+        <v>-2.208461606174505</v>
       </c>
       <c r="G44">
-        <v>-9.173231257839081</v>
+        <v>-7.035371038112233</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.670962482647173</v>
       </c>
       <c r="E45">
-        <v>-22.01372029636658</v>
+        <v>-20.7671355569571</v>
       </c>
       <c r="F45">
-        <v>-2.609563729549247</v>
+        <v>-2.698676181272807</v>
       </c>
       <c r="G45">
-        <v>-9.419257250366245</v>
+        <v>-6.983934608946378</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.704333157697145</v>
       </c>
       <c r="E46">
-        <v>-21.60934115290364</v>
+        <v>-20.57182700148029</v>
       </c>
       <c r="F46">
-        <v>-2.295489057145218</v>
+        <v>-2.437460461208817</v>
       </c>
       <c r="G46">
-        <v>-9.028782041127647</v>
+        <v>-7.071192133876691</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-4.728759050155887</v>
       </c>
       <c r="E47">
-        <v>-20.7722708464818</v>
+        <v>-19.1774600413045</v>
       </c>
       <c r="F47">
-        <v>-2.421082809288067</v>
+        <v>-2.990907633632417</v>
       </c>
       <c r="G47">
-        <v>-8.456153098238033</v>
+        <v>-6.715140220018227</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-4.740823722637435</v>
       </c>
       <c r="E48">
-        <v>-20.18975512097913</v>
+        <v>-19.79326005076355</v>
       </c>
       <c r="F48">
-        <v>-2.582876216933256</v>
+        <v>-2.469093327219521</v>
       </c>
       <c r="G48">
-        <v>-9.220920531984051</v>
+        <v>-7.187596749919552</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-4.742592586863042</v>
       </c>
       <c r="E49">
-        <v>-19.73237924620442</v>
+        <v>-19.01256018878919</v>
       </c>
       <c r="F49">
-        <v>-2.802574991136338</v>
+        <v>-3.041809982167043</v>
       </c>
       <c r="G49">
-        <v>-9.116544874178114</v>
+        <v>-6.105321911973866</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-4.735535556191396</v>
       </c>
       <c r="E50">
-        <v>-19.7034377688214</v>
+        <v>-18.33387326078563</v>
       </c>
       <c r="F50">
-        <v>-2.937533436767836</v>
+        <v>-2.644423086593856</v>
       </c>
       <c r="G50">
-        <v>-9.202046945574125</v>
+        <v>-6.916551443001621</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-4.726724677813052</v>
       </c>
       <c r="E51">
-        <v>-19.44164668643798</v>
+        <v>-17.8601903511093</v>
       </c>
       <c r="F51">
-        <v>-2.942065434828552</v>
+        <v>-2.820285486208191</v>
       </c>
       <c r="G51">
-        <v>-8.733337570693685</v>
+        <v>-6.05212018560903</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-4.721262041616358</v>
       </c>
       <c r="E52">
-        <v>-19.34559322426129</v>
+        <v>-16.78278487215238</v>
       </c>
       <c r="F52">
-        <v>-2.932627845008458</v>
+        <v>-3.267050534294854</v>
       </c>
       <c r="G52">
-        <v>-8.432098462985744</v>
+        <v>-6.28044726904455</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-4.726215667202724</v>
       </c>
       <c r="E53">
-        <v>-19.0165226035459</v>
+        <v>-17.0419177402933</v>
       </c>
       <c r="F53">
-        <v>-3.071018216789754</v>
+        <v>-3.096981736295699</v>
       </c>
       <c r="G53">
-        <v>-8.617871384016825</v>
+        <v>-6.331552294832901</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-4.745649470142962</v>
       </c>
       <c r="E54">
-        <v>-18.98821964099796</v>
+        <v>-18.15532005913719</v>
       </c>
       <c r="F54">
-        <v>-2.776320714672011</v>
+        <v>-3.363587643049706</v>
       </c>
       <c r="G54">
-        <v>-8.375579421624309</v>
+        <v>-6.683358307993445</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-4.783853953775427</v>
       </c>
       <c r="E55">
-        <v>-18.63616248621965</v>
+        <v>-17.2955439840409</v>
       </c>
       <c r="F55">
-        <v>-3.135257280509453</v>
+        <v>-3.44913894330863</v>
       </c>
       <c r="G55">
-        <v>-8.675145106336933</v>
+        <v>-6.547751983384713</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-4.84273447168676</v>
       </c>
       <c r="E56">
-        <v>-18.55863953968234</v>
+        <v>-15.63170564956468</v>
       </c>
       <c r="F56">
-        <v>-3.054785529164495</v>
+        <v>-3.007986912743337</v>
       </c>
       <c r="G56">
-        <v>-8.540779083477672</v>
+        <v>-6.263827881845963</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-4.921883278738727</v>
       </c>
       <c r="E57">
-        <v>-17.73878649143766</v>
+        <v>-17.28700328206243</v>
       </c>
       <c r="F57">
-        <v>-2.89201961818842</v>
+        <v>-3.653028325629284</v>
       </c>
       <c r="G57">
-        <v>-8.533320866873053</v>
+        <v>-6.596067970847537</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-5.019712114684402</v>
       </c>
       <c r="E58">
-        <v>-17.50699654935506</v>
+        <v>-16.16445797419706</v>
       </c>
       <c r="F58">
-        <v>-2.92178700080802</v>
+        <v>-3.622734101341503</v>
       </c>
       <c r="G58">
-        <v>-8.748257285124479</v>
+        <v>-6.890377138621931</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-5.130978148399143</v>
       </c>
       <c r="E59">
-        <v>-17.59322322293511</v>
+        <v>-17.01622317877378</v>
       </c>
       <c r="F59">
-        <v>-3.158161639196859</v>
+        <v>-3.169415010363891</v>
       </c>
       <c r="G59">
-        <v>-8.650102823395251</v>
+        <v>-6.448649248624805</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-5.252412830864023</v>
       </c>
       <c r="E60">
-        <v>-17.43766561229763</v>
+        <v>-16.13061215946373</v>
       </c>
       <c r="F60">
-        <v>-2.920335701118316</v>
+        <v>-3.026679851554911</v>
       </c>
       <c r="G60">
-        <v>-8.800635424877896</v>
+        <v>-6.961254805527496</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-5.377952122789262</v>
       </c>
       <c r="E61">
-        <v>-17.15565489346995</v>
+        <v>-15.83476242406862</v>
       </c>
       <c r="F61">
-        <v>-3.176850436171419</v>
+        <v>-3.25755992896098</v>
       </c>
       <c r="G61">
-        <v>-9.044400655750604</v>
+        <v>-7.030770765485892</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-5.506551925276554</v>
       </c>
       <c r="E62">
-        <v>-16.70456001214389</v>
+        <v>-14.9779253286033</v>
       </c>
       <c r="F62">
-        <v>-2.918249871998067</v>
+        <v>-3.037167811241755</v>
       </c>
       <c r="G62">
-        <v>-9.23132200432749</v>
+        <v>-6.891010414382904</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-5.633696995860197</v>
       </c>
       <c r="E63">
-        <v>-16.12119293352778</v>
+        <v>-15.11957146708922</v>
       </c>
       <c r="F63">
-        <v>-3.016724532108066</v>
+        <v>-3.309579745121984</v>
       </c>
       <c r="G63">
-        <v>-9.572382016880852</v>
+        <v>-6.574546438639139</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-5.761284804647209</v>
       </c>
       <c r="E64">
-        <v>-16.08658633516116</v>
+        <v>-15.8617928854204</v>
       </c>
       <c r="F64">
-        <v>-3.07918674774876</v>
+        <v>-3.075185733193238</v>
       </c>
       <c r="G64">
-        <v>-9.001633213944801</v>
+        <v>-8.332936666237766</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-5.887165641613313</v>
       </c>
       <c r="E65">
-        <v>-15.67051467181041</v>
+        <v>-16.80601594381173</v>
       </c>
       <c r="F65">
-        <v>-3.167401249207685</v>
+        <v>-3.078812325682695</v>
       </c>
       <c r="G65">
-        <v>-9.630613855896318</v>
+        <v>-7.730730792211316</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-6.017148314297534</v>
       </c>
       <c r="E66">
-        <v>-16.57619588792246</v>
+        <v>-15.0915719122998</v>
       </c>
       <c r="F66">
-        <v>-3.39896638645587</v>
+        <v>-3.288737192900145</v>
       </c>
       <c r="G66">
-        <v>-9.725828343108285</v>
+        <v>-7.201975062793038</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-6.151411689796165</v>
       </c>
       <c r="E67">
-        <v>-15.31296447806079</v>
+        <v>-16.26929667594863</v>
       </c>
       <c r="F67">
-        <v>-3.078557188522633</v>
+        <v>-3.479752089046489</v>
       </c>
       <c r="G67">
-        <v>-9.406768921110999</v>
+        <v>-7.855312212380314</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-6.297124085566535</v>
       </c>
       <c r="E68">
-        <v>-15.34761183269348</v>
+        <v>-15.15747932300743</v>
       </c>
       <c r="F68">
-        <v>-3.04180584033003</v>
+        <v>-3.234822072121537</v>
       </c>
       <c r="G68">
-        <v>-9.489390079977817</v>
+        <v>-8.282310698797092</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-6.453464090966314</v>
       </c>
       <c r="E69">
-        <v>-15.67712624386161</v>
+        <v>-14.5127016083733</v>
       </c>
       <c r="F69">
-        <v>-3.172221519124575</v>
+        <v>-3.38578706107733</v>
       </c>
       <c r="G69">
-        <v>-9.533089388706502</v>
+        <v>-7.614933202156953</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-6.625378306072458</v>
       </c>
       <c r="E70">
-        <v>-16.32069032746169</v>
+        <v>-14.96681245338848</v>
       </c>
       <c r="F70">
-        <v>-3.213851122952264</v>
+        <v>-3.991519955598232</v>
       </c>
       <c r="G70">
-        <v>-9.654251776010558</v>
+        <v>-8.114906056055782</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-6.809074797333285</v>
       </c>
       <c r="E71">
-        <v>-16.78215088579131</v>
+        <v>-15.88294085903622</v>
       </c>
       <c r="F71">
-        <v>-3.330331176929514</v>
+        <v>-3.499679295288234</v>
       </c>
       <c r="G71">
-        <v>-9.447242789046751</v>
+        <v>-7.750552651651923</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-7.005105926884815</v>
       </c>
       <c r="E72">
-        <v>-17.0306373115402</v>
+        <v>-14.50299708857487</v>
       </c>
       <c r="F72">
-        <v>-3.313130127810382</v>
+        <v>-3.823517934269062</v>
       </c>
       <c r="G72">
-        <v>-9.429776846685826</v>
+        <v>-8.249062080735239</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-7.206010241512515</v>
       </c>
       <c r="E73">
-        <v>-16.61359655475181</v>
+        <v>-15.77539412982806</v>
       </c>
       <c r="F73">
-        <v>-3.11039797475144</v>
+        <v>-3.480345200106894</v>
       </c>
       <c r="G73">
-        <v>-9.216563069753107</v>
+        <v>-7.220454902615831</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-7.407629789682987</v>
       </c>
       <c r="E74">
-        <v>-16.71597176664321</v>
+        <v>-15.44860586001254</v>
       </c>
       <c r="F74">
-        <v>-3.185457173486506</v>
+        <v>-3.351858788993468</v>
       </c>
       <c r="G74">
-        <v>-8.44606334194274</v>
+        <v>-7.447702464158294</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-7.600737344841355</v>
       </c>
       <c r="E75">
-        <v>-17.12980183536016</v>
+        <v>-15.18884806245856</v>
       </c>
       <c r="F75">
-        <v>-3.533092322847555</v>
+        <v>-3.246261825954198</v>
       </c>
       <c r="G75">
-        <v>-9.059238339642413</v>
+        <v>-7.199100712706965</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-7.775896430343264</v>
       </c>
       <c r="E76">
-        <v>-17.18633983334593</v>
+        <v>-16.65069381382265</v>
       </c>
       <c r="F76">
-        <v>-3.35994034137518</v>
+        <v>-3.692732803612867</v>
       </c>
       <c r="G76">
-        <v>-8.959787795397203</v>
+        <v>-7.998819718504188</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-7.922757867376576</v>
       </c>
       <c r="E77">
-        <v>-17.24145589049328</v>
+        <v>-15.98803768380624</v>
       </c>
       <c r="F77">
-        <v>-3.264492535755009</v>
+        <v>-3.908175426100365</v>
       </c>
       <c r="G77">
-        <v>-8.521449407270982</v>
+        <v>-6.203758558757208</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-8.032214284150946</v>
       </c>
       <c r="E78">
-        <v>-17.98162138162498</v>
+        <v>-16.00683537941208</v>
       </c>
       <c r="F78">
-        <v>-3.608979060618017</v>
+        <v>-3.834574153994226</v>
       </c>
       <c r="G78">
-        <v>-8.918129406478492</v>
+        <v>-6.754547690947157</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-8.101291897029194</v>
       </c>
       <c r="E79">
-        <v>-18.41423103205174</v>
+        <v>-17.37462925411085</v>
       </c>
       <c r="F79">
-        <v>-3.604054416408375</v>
+        <v>-4.384784894975088</v>
       </c>
       <c r="G79">
-        <v>-8.60277448362182</v>
+        <v>-7.309717253918965</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-8.12699617321395</v>
       </c>
       <c r="E80">
-        <v>-18.72969811684808</v>
+        <v>-17.48392850275998</v>
       </c>
       <c r="F80">
-        <v>-3.805577981426632</v>
+        <v>-4.001198600332541</v>
       </c>
       <c r="G80">
-        <v>-8.106611127953506</v>
+        <v>-8.075829988504355</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-8.114628821394994</v>
       </c>
       <c r="E81">
-        <v>-18.99838153667118</v>
+        <v>-19.09590222442636</v>
       </c>
       <c r="F81">
-        <v>-4.009137673520971</v>
+        <v>-4.43375052052197</v>
       </c>
       <c r="G81">
-        <v>-7.465788557393953</v>
+        <v>-6.689136539159627</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-8.067209172270255</v>
       </c>
       <c r="E82">
-        <v>-20.29577575444671</v>
+        <v>-17.95650193630443</v>
       </c>
       <c r="F82">
-        <v>-4.136646611099094</v>
+        <v>-4.282247092754358</v>
       </c>
       <c r="G82">
-        <v>-7.914676072833788</v>
+        <v>-6.757550008674049</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-7.99730399587428</v>
       </c>
       <c r="E83">
-        <v>-20.47780229565903</v>
+        <v>-20.13758257193676</v>
       </c>
       <c r="F83">
-        <v>-4.166499315561182</v>
+        <v>-3.597802727619447</v>
       </c>
       <c r="G83">
-        <v>-8.286671442249595</v>
+        <v>-7.009534699553165</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-7.913189529263135</v>
       </c>
       <c r="E84">
-        <v>-21.44267972399934</v>
+        <v>-21.5819257712612</v>
       </c>
       <c r="F84">
-        <v>-4.46987065275364</v>
+        <v>-4.408636905971298</v>
       </c>
       <c r="G84">
-        <v>-8.415118141415617</v>
+        <v>-6.120950370261501</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-7.832130976179458</v>
       </c>
       <c r="E85">
-        <v>-23.6903108136484</v>
+        <v>-21.17280531551223</v>
       </c>
       <c r="F85">
-        <v>-4.589121595693254</v>
+        <v>-4.387569037815898</v>
       </c>
       <c r="G85">
-        <v>-7.628569958958006</v>
+        <v>-5.574938696662104</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-7.763716326790989</v>
       </c>
       <c r="E86">
-        <v>-23.48283424851297</v>
+        <v>-22.69835311074221</v>
       </c>
       <c r="F86">
-        <v>-4.141198489977477</v>
+        <v>-4.805351167213412</v>
       </c>
       <c r="G86">
-        <v>-7.760360222893103</v>
+        <v>-6.962987290510883</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-7.724992599542515</v>
       </c>
       <c r="E87">
-        <v>-24.55892647000766</v>
+        <v>-24.00460955215075</v>
       </c>
       <c r="F87">
-        <v>-4.661445525264276</v>
+        <v>-4.461606859543312</v>
       </c>
       <c r="G87">
-        <v>-7.957492732962982</v>
+        <v>-6.023770431335428</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-7.723162115236701</v>
       </c>
       <c r="E88">
-        <v>-25.96748566772349</v>
+        <v>-24.15682514897058</v>
       </c>
       <c r="F88">
-        <v>-4.543795816514273</v>
+        <v>-4.615335282154844</v>
       </c>
       <c r="G88">
-        <v>-7.638748308235403</v>
+        <v>-5.931728885371443</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-7.771853814917804</v>
       </c>
       <c r="E89">
-        <v>-27.92370492650494</v>
+        <v>-26.99838824709564</v>
       </c>
       <c r="F89">
-        <v>-4.369142833308025</v>
+        <v>-4.945187868479996</v>
       </c>
       <c r="G89">
-        <v>-7.647597762781226</v>
+        <v>-6.447011919066642</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-7.873993309989059</v>
       </c>
       <c r="E90">
-        <v>-28.9270426845924</v>
+        <v>-28.16327478693273</v>
       </c>
       <c r="F90">
-        <v>-4.618231254595032</v>
+        <v>-4.983364836972817</v>
       </c>
       <c r="G90">
-        <v>-7.799049106300515</v>
+        <v>-6.660422569292926</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-8.037504735353648</v>
       </c>
       <c r="E91">
-        <v>-30.8194625373168</v>
+        <v>-29.95381982414357</v>
       </c>
       <c r="F91">
-        <v>-4.892973385979335</v>
+        <v>-4.812600210355311</v>
       </c>
       <c r="G91">
-        <v>-8.165420461963434</v>
+        <v>-6.885514368270834</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-8.258573396650045</v>
       </c>
       <c r="E92">
-        <v>-32.27952180568485</v>
+        <v>-31.44768867945289</v>
       </c>
       <c r="F92">
-        <v>-4.765234990630637</v>
+        <v>-4.505244425955388</v>
       </c>
       <c r="G92">
-        <v>-8.711556821982091</v>
+        <v>-6.902917967422129</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-8.536659912317905</v>
       </c>
       <c r="E93">
-        <v>-34.10035101282199</v>
+        <v>-33.79710175089834</v>
       </c>
       <c r="F93">
-        <v>-4.914315443745061</v>
+        <v>-4.985969224087219</v>
       </c>
       <c r="G93">
-        <v>-8.528425284306362</v>
+        <v>-6.703567351578065</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-8.859993712495028</v>
       </c>
       <c r="E94">
-        <v>-35.66651469142676</v>
+        <v>-35.91856502621969</v>
       </c>
       <c r="F94">
-        <v>-4.871499617796563</v>
+        <v>-5.147463591099997</v>
       </c>
       <c r="G94">
-        <v>-8.767334307271092</v>
+        <v>-7.918055731040016</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-9.219464508324805</v>
       </c>
       <c r="E95">
-        <v>-38.54921897591151</v>
+        <v>-38.48972614863574</v>
       </c>
       <c r="F95">
-        <v>-4.661433928120637</v>
+        <v>-5.088781215918277</v>
       </c>
       <c r="G95">
-        <v>-8.960962472715483</v>
+        <v>-8.836797767684535</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-9.599832820669452</v>
       </c>
       <c r="E96">
-        <v>-39.32445976246962</v>
+        <v>-40.77281066129084</v>
       </c>
       <c r="F96">
-        <v>-4.775758570115802</v>
+        <v>-5.237578367380944</v>
       </c>
       <c r="G96">
-        <v>-9.074115398192935</v>
+        <v>-8.550550561281698</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-9.985001575080354</v>
       </c>
       <c r="E97">
-        <v>-41.9114682796755</v>
+        <v>-42.05462466424299</v>
       </c>
       <c r="F97">
-        <v>-4.59467745586383</v>
+        <v>-5.012607034659043</v>
       </c>
       <c r="G97">
-        <v>-9.889748328553464</v>
+        <v>-8.244986803558408</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-10.3619573319062</v>
       </c>
       <c r="E98">
-        <v>-44.58317058200985</v>
+        <v>-44.00800004134762</v>
       </c>
       <c r="F98">
-        <v>-4.618332315418173</v>
+        <v>-4.861087867910777</v>
       </c>
       <c r="G98">
-        <v>-10.22584713410895</v>
+        <v>-8.246187730649165</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-10.71124027320869</v>
       </c>
       <c r="E99">
-        <v>-46.41819655516103</v>
+        <v>-46.74748907110278</v>
       </c>
       <c r="F99">
-        <v>-4.589063609975058</v>
+        <v>-5.227652040793197</v>
       </c>
       <c r="G99">
-        <v>-10.00540810730233</v>
+        <v>-8.924632787609312</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-11.02381590382288</v>
       </c>
       <c r="E100">
-        <v>-48.99622284417271</v>
+        <v>-48.60035836396269</v>
       </c>
       <c r="F100">
-        <v>-4.46752720137112</v>
+        <v>-4.838194277999607</v>
       </c>
       <c r="G100">
-        <v>-10.98496758555116</v>
+        <v>-9.956576968054675</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-11.27241978273887</v>
       </c>
       <c r="E101">
-        <v>-51.50100333034732</v>
+        <v>-51.55919535346438</v>
       </c>
       <c r="F101">
-        <v>-4.506000725394143</v>
+        <v>-5.093727397680393</v>
       </c>
       <c r="G101">
-        <v>-11.67619300048534</v>
+        <v>-11.03957367474344</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-11.45759095829289</v>
       </c>
       <c r="E102">
-        <v>-53.10657492188535</v>
+        <v>-54.09146028051005</v>
       </c>
       <c r="F102">
-        <v>-4.357587936406375</v>
+        <v>-4.935075987594023</v>
       </c>
       <c r="G102">
-        <v>-11.64332172290283</v>
+        <v>-10.43568125283544</v>
       </c>
     </row>
   </sheetData>
